--- a/examples/lab-inventory.xlsx
+++ b/examples/lab-inventory.xlsx
@@ -14,17 +14,19 @@
     <sheet name="Links" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Hosts" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Interfaces" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Gaps" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Hardware" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Gaps" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$B$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Devices'!$A$1:$V$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$B$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Devices'!$A$1:$W$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'IPAM'!$A$1:$J$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'VLANs'!$A$1:$D$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Links'!$A$1:$H$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Hosts'!$A$1:$L$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Interfaces'!$A$1:$K$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Gaps'!$A$1:$D$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Interfaces'!$A$1:$N$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Hardware'!$A$1:$K$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Gaps'!$A$1:$D$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -468,7 +470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:51:54</t>
+          <t>2026-09-30 02:01:43</t>
         </is>
       </c>
     </row>
@@ -622,68 +624,78 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  windows</t>
+          <t xml:space="preserve">  wireless</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Links by kind</t>
-        </is>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  phone</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  member</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>12</v>
+          <t>Links by kind</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  lldp</t>
+          <t xml:space="preserve">  member</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  fdb</t>
+          <t xml:space="preserve">  lldp</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t xml:space="preserve">  fdb</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t xml:space="preserve">  cdp</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="B29" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B28"/>
+  <autoFilter ref="A1:B29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -694,7 +706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:W4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -702,23 +714,24 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
-    <col width="41" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="41" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="9" customWidth="1" min="15" max="15"/>
     <col width="9" customWidth="1" min="16" max="16"/>
     <col width="9" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="9" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="40" customWidth="1" min="22" max="22"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="40" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -749,85 +762,90 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>OS version</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Serial</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Contact</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>OS / sysDescr</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>All IPs</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Interfaces</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>VLANs</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>LLDP</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>CDP</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>ARP</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Routes</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>FDB</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Uptime (days)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Depth</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Discovered via</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Credential</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Errors</t>
         </is>
@@ -861,49 +879,51 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>17.6.4</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>FDO2222R1XX</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>DC1</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>netops@example.test</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Cisco IOS Software, ISR4300 Software (X86_64_LINUX_IOSD-UNIVERSALK9-M), Version 17.6.4</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>10.0.0.1 203.0.113.2</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>2</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
         <v>1</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>2</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>4</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -911,17 +931,20 @@
       <c r="S2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>lab</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -951,67 +974,72 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>16.12.4</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>FOC1234SW1X</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>DC1</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>netops@example.test</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Cisco IOS Software, IOS-XE Software, Catalyst L3 Switch Software (CAT3K_CAA-UNIVERSALK9-M), Version 16.12.4</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>10.0.0.2 10.1.0.1 10.2.0.1 192.168.99.1</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>7</v>
-      </c>
-      <c r="L3" t="n">
-        <v>3</v>
       </c>
       <c r="M3" t="n">
         <v>3</v>
       </c>
       <c r="N3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" t="n">
         <v>1</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>8</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>3</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>8</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>1</v>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>cdp:core-rtr</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>lab</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1041,70 +1069,75 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>YA.16.10.0016</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>CN51ABC123</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>DC1</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>netops@example.test</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>HP J9772A 2530-48G-PoEP Switch, revision YA.16.10.0016, ROM YA.15.20</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>10.1.0.2</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>6</v>
-      </c>
       <c r="L4" t="n">
+        <v>9</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>2</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>17</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>2</v>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>lldp:dist-sw1</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>lab</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V4"/>
+  <autoFilter ref="A1:W4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1774,10 +1807,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
@@ -1937,7 +1970,11 @@
           <t>10.1.0.60</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ap-lobby</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>aa:bb:cc:00:00:01</t>
@@ -1946,7 +1983,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>wireless</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1975,7 +2012,11 @@
           <t>10.1.0.90</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SEPAABBCC000002</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>aa:bb:cc:00:00:02</t>
@@ -1984,7 +2025,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2013,24 +2054,16 @@
           <t>10.2.0.10</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>srv-files</t>
-        </is>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>de:ad:be:ef:00:0c</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Dell Inc.</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>windows</t>
+          <t>host</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2051,14 +2084,10 @@
       <c r="I6" t="n">
         <v>20</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>445/microsoft-ds 3389/ms-wbt-server</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>arp sweep</t>
+          <t>arp</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -2075,7 +2104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2088,7 +2117,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2144,6 +2176,21 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>VLAN</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Mode</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LAG</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Addresses</t>
         </is>
       </c>
@@ -2195,7 +2242,10 @@
           <t>up</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
         <is>
           <t>10.0.0.1/30</t>
         </is>
@@ -2248,7 +2298,10 @@
           <t>up</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
         <is>
           <t>203.0.113.2/30</t>
         </is>
@@ -2301,7 +2354,10 @@
           <t>up</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
         <is>
           <t>10.0.0.2/30</t>
         </is>
@@ -2354,7 +2410,16 @@
           <t>up</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>trunk</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2403,7 +2468,16 @@
           <t>up</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>20</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2448,7 +2522,10 @@
           <t>up</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
         <is>
           <t>10.1.0.1/24</t>
         </is>
@@ -2497,7 +2574,10 @@
           <t>up</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
         <is>
           <t>10.2.0.1/24</t>
         </is>
@@ -2550,7 +2630,16 @@
           <t>up</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="n">
+        <v>10</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2595,7 +2684,10 @@
           <t>up</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
         <is>
           <t>192.168.99.1/24</t>
         </is>
@@ -2644,7 +2736,16 @@
           <t>up</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2689,7 +2790,16 @@
           <t>up</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2734,7 +2844,16 @@
           <t>up</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>10</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2779,7 +2898,16 @@
           <t>up</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>10</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2793,22 +2921,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>00:11:22:33:55:18</t>
+          <t>00:11:22:33:55:15</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -2825,6 +2953,13 @@
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Trk1</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2838,26 +2973,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VLAN10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>VLAN10</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>mgmt</t>
-        </is>
-      </c>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>00:11:22:33:44:20</t>
+          <t>00:11:22:33:55:16</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -2873,19 +3004,749 @@
           <t>up</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Trk1</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>10.1.0.2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>acc-sw2</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>24</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>00:11:22:33:55:18</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>trunk</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>10.1.0.2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>acc-sw2</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>100</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VLAN10</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>VLAN10</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>mgmt</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>00:11:22:33:44:20</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
         <is>
           <t>10.1.0.2/24</t>
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>10.1.0.2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>acc-sw2</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>289</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Trk1</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Trk1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>nas-01</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>00:11:22:33:55:f1</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>20</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K16"/>
+  <autoFilter ref="A1:N19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Device name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Serial</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>HW rev</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>FW rev</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>SW rev</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>FRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>10.0.0.1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>core-rtr</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>chassis</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Chassis</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ISR4331/K9</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ISR4331/K9</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>FDO2222R1XX</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>10.0.0.2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>dist-sw1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>stack</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c38xx Stack</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c38xx Stack</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>10.0.0.2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>dist-sw1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>chassis</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Switch 1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>WS-C3850-24T-S</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>WS-C3850-24T</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>FOC1234SW1X</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>V07</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>16.12.2r</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>16.12.4</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>10.0.0.2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>dist-sw1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>powerSupply</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Switch 1 - Power Supply A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Switch 1 - Power Supply A</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>PWR-C1-350WAC</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LIT21330ABC</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>V02</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>10.0.0.2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>dist-sw1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>fan</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Switch 1 - FAN - T1 1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Switch 1 - FAN - T1 1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>10.0.0.2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>dist-sw1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>module</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Switch 1 FRU Uplink Module 1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4x10G Uplink Module</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>C3850-NM-4-10G</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>FOC2210X1AB</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>V01</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>10.0.0.2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>dist-sw1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>port</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>subslot 1/1 transceiver 1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SFP-10GBase-SR</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SFP-10G-SR</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>AVD2045K1LM</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>V03</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>10.0.0.2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>dist-sw1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>chassis</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Switch 2</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>WS-C3850-24T-S</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>WS-C3850-24T</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>FOC1234SW2Y</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>V07</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>16.12.2r</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>16.12.4</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>10.0.0.2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dist-sw1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>powerSupply</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Switch 2 - Power Supply A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Switch 2 - Power Supply A</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>PWR-C1-350WAC</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>LIT21330DEF</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>V02</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10.1.0.2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>acc-sw2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>chassis</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Chassis</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>J9772A</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>J9772A</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>CN51ABC123</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K11"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/examples/lab-inventory.xlsx
+++ b/examples/lab-inventory.xlsx
@@ -470,7 +470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-30 02:01:43</t>
+          <t>2026-09-30 13:00:08</t>
         </is>
       </c>
     </row>
